--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2021_maule.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2021_maule.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:37</t>
+    <t xml:space="preserve">2026-10-05 01:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -726,7 +726,7 @@
         <v>612080.25</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -734,10 +734,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>619152.12</v>
+        <v>619152.13</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -767,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>617417.12</v>
+        <v>617417.13</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>805474.38</v>
@@ -836,7 +836,7 @@
         <v>619176.06</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -913,7 +913,7 @@
         <v>659349.81</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -943,7 +943,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>647634.12</v>
+        <v>647634.13</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>864071.75</v>
@@ -1001,7 +1001,7 @@
         <v>687736.06</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>685707.5</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1166,7 +1166,7 @@
         <v>765073.44</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1273,7 +1273,7 @@
         <v>55</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>818310.62</v>
+        <v>818310.63</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>1035374.06</v>
@@ -1287,7 +1287,7 @@
         <v>833997.81</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>834394.69</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1328,7 +1328,7 @@
         <v>60</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>855612.62</v>
+        <v>855612.63</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>1086115.25</v>
@@ -1342,7 +1342,7 @@
         <v>833343.94</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1364,7 +1364,7 @@
         <v>904886</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1383,7 +1383,7 @@
         <v>65</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>920151.12</v>
+        <v>920151.13</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>1158414.88</v>
@@ -1416,10 +1416,10 @@
         <v>68</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>955682.62</v>
+        <v>955682.63</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1518,7 +1518,7 @@
         <v>978389.69</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1551,7 +1551,7 @@
         <v>1001845.06</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1562,7 +1562,7 @@
         <v>1019536</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1584,7 +1584,7 @@
         <v>1060850.5</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
@@ -1614,7 +1614,7 @@
         <v>86</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>1084456.12</v>
+        <v>1084456.13</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>1353554.88</v>
